--- a/documentos/Estandarizacion de la informacion.xlsx
+++ b/documentos/Estandarizacion de la informacion.xlsx
@@ -513,7 +513,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>PErro</t>
+          <t>PÉrro</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
@@ -538,7 +538,7 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>JuaN PÉrEz</t>
+          <t>JUaN PÉREz</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
@@ -563,7 +563,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>vEntAS</t>
+          <t>VEnTAS</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -588,7 +588,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>markEtiNg</t>
+          <t>markEtinG</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Fb.I</t>
+          <t>F.b.i</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -663,7 +663,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>fERNanda cRUz</t>
+          <t>fERnAnDa cRUz</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
@@ -688,12 +688,12 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>SiLA</t>
+          <t>sILla</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>Sila</t>
+          <t>Silla</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
@@ -713,7 +713,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>EdSoN CoVaRRuBias</t>
+          <t>EdSOn CoVaRruBias</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -738,12 +738,12 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>CeO</t>
+          <t>Ceo</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>Ceo</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
@@ -813,12 +813,12 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>JoEL COBlan</t>
+          <t>JoEl COBIan</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>Joel Coblan</t>
+          <t>Joel Cobian</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>EL UnIVerSal</t>
+          <t>EL UnIVeRSaL</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>vIctor caMpoS</t>
+          <t>VIcToR cAMPOs</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>CARlo</t>
+          <t>CARro</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>Carlo</t>
+          <t>Carro</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>Persona</t>
+          <t>Objeto/cosa</t>
         </is>
       </c>
     </row>
@@ -938,7 +938,7 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>CELULAR</t>
+          <t>CeLULAR</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
@@ -963,12 +963,12 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>VICtor MANuel VicENte</t>
+          <t>ViCtOr MaNuEl ViCENte</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>Víctor Manuel Vicente</t>
+          <t>Victor Manuel Vicente</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -988,7 +988,7 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>GOLondRinA</t>
+          <t>GoLonDRinA</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">

--- a/documentos/Estandarizacion de la informacion.xlsx
+++ b/documentos/Estandarizacion de la informacion.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hoja1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Hoja1'!$A$1:$E$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Hoja1'!$A$3:$E$23</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -31,15 +31,39 @@
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Calibri"/>
-      <color rgb="001A1A1A"/>
+      <color rgb="001F2933"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="001F4E79"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="001E7A46"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00B03A2E"/>
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -48,12 +72,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="001B3A4B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="001F4E79"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D6E3F0"/>
+        <fgColor rgb="00E7F0F7"/>
       </patternFill>
     </fill>
     <fill>
@@ -62,7 +91,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -70,40 +99,60 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border/>
     <border>
       <left style="thin">
-        <color rgb="00B0B8C4"/>
+        <color rgb="00D5DEE7"/>
       </left>
       <right style="thin">
-        <color rgb="00B0B8C4"/>
+        <color rgb="00D5DEE7"/>
       </right>
       <top style="thin">
-        <color rgb="00B0B8C4"/>
+        <color rgb="00D5DEE7"/>
       </top>
       <bottom style="thin">
-        <color rgb="00B0B8C4"/>
+        <color rgb="00D5DEE7"/>
       </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -467,557 +516,565 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="001F4E79"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
     <col width="28" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
+    <row r="1" ht="38" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>Estandarización de la información</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+    </row>
+    <row r="2" ht="10" customHeight="1"/>
+    <row r="3" ht="26" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
           <t>No.</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>Texto</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>Corrección</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>Función</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>Clasificación</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="2" t="n">
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>PÉrro</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>Perro</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>NOMPROPIO</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>NOMPROPIO</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>Objeto/cosa</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="4" t="n">
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B5" s="8" t="inlineStr">
         <is>
           <t>JUaN PÉREz</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C5" s="8" t="inlineStr">
         <is>
           <t>Juan Pérez</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>NOMPROPIO</t>
-        </is>
-      </c>
-      <c r="E3" s="5" t="inlineStr">
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>NOMPROPIO</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="inlineStr">
         <is>
           <t>Persona</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="2" t="n">
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>VEnTAS</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>Ventas</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D6" s="10" t="inlineStr">
         <is>
           <t>MINUSC</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>Objeto/cosa</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="4" t="n">
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B7" s="8" t="inlineStr">
         <is>
           <t>markEtinG</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C7" s="8" t="inlineStr">
         <is>
           <t>Marketing</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>NOMPROPIO</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>NOMPROPIO</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
         <is>
           <t>Objeto/cosa</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="2" t="n">
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>F.b.i</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
         <is>
           <t>FBI</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D8" s="11" t="inlineStr">
         <is>
           <t>MAYUSC</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="E8" s="5" t="inlineStr">
         <is>
           <t>Acrónimo</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="4" t="n">
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B9" s="8" t="inlineStr">
         <is>
           <t>pRoHIBIDO pASAR</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C9" s="8" t="inlineStr">
         <is>
           <t>Prohibido Pasar</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D9" s="12" t="inlineStr">
         <is>
           <t>MAYUSC</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="E9" s="8" t="inlineStr">
         <is>
           <t>Aviso</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="2" t="n">
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>fERnAnDa cRUz</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
         <is>
           <t>Fernanda Cruz</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>NOMPROPIO</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>NOMPROPIO</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
         <is>
           <t>Persona</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="4" t="n">
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B11" s="8" t="inlineStr">
         <is>
           <t>sILla</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C11" s="8" t="inlineStr">
         <is>
           <t>Silla</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>NOMPROPIO</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>NOMPROPIO</t>
+        </is>
+      </c>
+      <c r="E11" s="8" t="inlineStr">
         <is>
           <t>Objeto/cosa</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="2" t="n">
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>EdSOn CoVaRruBias</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C12" s="5" t="inlineStr">
         <is>
           <t>Edson Covarrubias</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>NOMPROPIO</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>NOMPROPIO</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
         <is>
           <t>Persona</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="4" t="n">
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B13" s="8" t="inlineStr">
         <is>
           <t>Ceo</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C13" s="8" t="inlineStr">
         <is>
           <t>Ceo</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D13" s="12" t="inlineStr">
         <is>
           <t>MAYUSC</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr">
+      <c r="E13" s="8" t="inlineStr">
         <is>
           <t>Acrónimo</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="2" t="n">
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>CasCO</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C14" s="5" t="inlineStr">
         <is>
           <t>Casco</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>NOMPROPIO</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="inlineStr">
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>NOMPROPIO</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
         <is>
           <t>Objeto/cosa</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="4" t="n">
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B15" s="8" t="inlineStr">
         <is>
           <t>VENTiLaDor</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr">
+      <c r="C15" s="8" t="inlineStr">
         <is>
           <t>Ventilador</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>NOMPROPIO</t>
-        </is>
-      </c>
-      <c r="E13" s="5" t="inlineStr">
+      <c r="D15" s="9" t="inlineStr">
+        <is>
+          <t>NOMPROPIO</t>
+        </is>
+      </c>
+      <c r="E15" s="8" t="inlineStr">
         <is>
           <t>Objeto/cosa</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="2" t="n">
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>JoEl COBIan</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C16" s="5" t="inlineStr">
         <is>
           <t>Joel Cobian</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>NOMPROPIO</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="inlineStr">
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>NOMPROPIO</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
         <is>
           <t>Persona</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="4" t="n">
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="7" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B17" s="8" t="inlineStr">
         <is>
           <t>IVA</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr">
+      <c r="C17" s="8" t="inlineStr">
         <is>
           <t>Iva</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D17" s="12" t="inlineStr">
         <is>
           <t>MAYUSC</t>
         </is>
       </c>
-      <c r="E15" s="5" t="inlineStr">
+      <c r="E17" s="8" t="inlineStr">
         <is>
           <t>Acrónimo</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="2" t="n">
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>EL UnIVeRSaL</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C18" s="5" t="inlineStr">
         <is>
           <t>El Universal</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>NOMPROPIO</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="inlineStr">
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>NOMPROPIO</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
         <is>
           <t>Nombre propio</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="4" t="n">
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="7" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B19" s="8" t="inlineStr">
         <is>
           <t>VIcToR cAMPOs</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr">
+      <c r="C19" s="8" t="inlineStr">
         <is>
           <t>Victor Campos</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
-        <is>
-          <t>NOMPROPIO</t>
-        </is>
-      </c>
-      <c r="E17" s="5" t="inlineStr">
+      <c r="D19" s="9" t="inlineStr">
+        <is>
+          <t>NOMPROPIO</t>
+        </is>
+      </c>
+      <c r="E19" s="8" t="inlineStr">
         <is>
           <t>Persona</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="2" t="n">
+    <row r="20" ht="22" customHeight="1">
+      <c r="A20" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B20" s="5" t="inlineStr">
         <is>
           <t>CARro</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="C20" s="5" t="inlineStr">
         <is>
           <t>Carro</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>NOMPROPIO</t>
-        </is>
-      </c>
-      <c r="E18" s="3" t="inlineStr">
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>NOMPROPIO</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
         <is>
           <t>Objeto/cosa</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="4" t="n">
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="7" t="n">
         <v>18</v>
       </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="B21" s="8" t="inlineStr">
         <is>
           <t>CeLULAR</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr">
+      <c r="C21" s="8" t="inlineStr">
         <is>
           <t>Celular</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
-        <is>
-          <t>NOMPROPIO</t>
-        </is>
-      </c>
-      <c r="E19" s="5" t="inlineStr">
+      <c r="D21" s="9" t="inlineStr">
+        <is>
+          <t>NOMPROPIO</t>
+        </is>
+      </c>
+      <c r="E21" s="8" t="inlineStr">
         <is>
           <t>Objeto/cosa</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="2" t="n">
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="4" t="n">
         <v>19</v>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B22" s="5" t="inlineStr">
         <is>
           <t>ViCtOr MaNuEl ViCENte</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="C22" s="5" t="inlineStr">
         <is>
           <t>Victor Manuel Vicente</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>NOMPROPIO</t>
-        </is>
-      </c>
-      <c r="E20" s="3" t="inlineStr">
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>NOMPROPIO</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
         <is>
           <t>Persona</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="4" t="n">
+    <row r="23" ht="22" customHeight="1">
+      <c r="A23" s="7" t="n">
         <v>20</v>
       </c>
-      <c r="B21" s="5" t="inlineStr">
+      <c r="B23" s="8" t="inlineStr">
         <is>
           <t>GoLonDRinA</t>
         </is>
       </c>
-      <c r="C21" s="5" t="inlineStr">
+      <c r="C23" s="8" t="inlineStr">
         <is>
           <t>Golondrina</t>
         </is>
       </c>
-      <c r="D21" s="4" t="inlineStr">
-        <is>
-          <t>NOMPROPIO</t>
-        </is>
-      </c>
-      <c r="E21" s="5" t="inlineStr">
+      <c r="D23" s="9" t="inlineStr">
+        <is>
+          <t>NOMPROPIO</t>
+        </is>
+      </c>
+      <c r="E23" s="8" t="inlineStr">
         <is>
           <t>Animal</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E21"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="3" fitToHeight="1" fitToWidth="1"/>
-  <headerFooter>
-    <oddHeader>&amp;CHoja1</oddHeader>
-    <oddFooter/>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
+  <autoFilter ref="A3:E23"/>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
+  <pageSetup orientation="portrait" paperSize="3" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
 </file>
--- a/documentos/Estandarizacion de la informacion.xlsx
+++ b/documentos/Estandarizacion de la informacion.xlsx
@@ -7,10 +7,11 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hoja1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Estandarización" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Hoja1'!$A$3:$E$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Estandarización'!$A$2:$E$22</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Estandarización'!$1:$2</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -19,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -31,7 +32,7 @@
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="18"/>
+      <sz val="16"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -41,7 +42,13 @@
     </font>
     <font>
       <name val="Calibri"/>
-      <color rgb="001F2933"/>
+      <color rgb="00000000"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
       <sz val="11"/>
     </font>
     <font>
@@ -59,11 +66,23 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00B03A2E"/>
+      <color rgb="00A93226"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="001B3A4B"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="001F2933"/>
+      <sz val="12"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -72,17 +91,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001B3A4B"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="001F4E79"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E7F0F7"/>
       </patternFill>
     </fill>
     <fill>
@@ -90,8 +99,13 @@
         <fgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F7F9FB"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -99,60 +113,68 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border/>
     <border>
       <left style="thin">
-        <color rgb="00D5DEE7"/>
+        <color rgb="00000000"/>
       </left>
       <right style="thin">
-        <color rgb="00D5DEE7"/>
+        <color rgb="00000000"/>
       </right>
       <top style="thin">
-        <color rgb="00D5DEE7"/>
+        <color rgb="00000000"/>
       </top>
       <bottom style="thin">
-        <color rgb="00D5DEE7"/>
+        <color rgb="00000000"/>
       </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -520,20 +542,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
     <col width="28" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="38" customHeight="1">
+    <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Estandarización de la información</t>
+          <t>PRODUCTO 9. ESTANDARIZACIÓN DE INFORMACIÓN</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -541,540 +563,571 @@
       <c r="D1" s="2" t="n"/>
       <c r="E1" s="2" t="n"/>
     </row>
-    <row r="2" ht="10" customHeight="1"/>
-    <row r="3" ht="26" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>No.</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>Texto</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>Corrección</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>Función</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>Clasificación</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="22" customHeight="1">
-      <c r="A4" s="4" t="n">
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>TEXTO</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>CORRECCIÓN</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>FUNCIÓN</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>CLASIFICACIÓN</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>PÉrro</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="inlineStr">
-        <is>
-          <t>Perro</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>JuanN Pérez</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Juan Pérez</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
         <is>
           <t>NOMPROPIO</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>Persona</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>vEntAS</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>ventas</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>MINUSC</t>
+        </is>
+      </c>
+      <c r="E4" s="8" t="inlineStr">
         <is>
           <t>Objeto/cosa</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="B5" s="8" t="inlineStr">
-        <is>
-          <t>JUaN PÉREz</t>
-        </is>
-      </c>
-      <c r="C5" s="8" t="inlineStr">
-        <is>
-          <t>Juan Pérez</t>
-        </is>
-      </c>
-      <c r="D5" s="9" t="inlineStr">
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>markEtiNg</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>marketing</t>
+        </is>
+      </c>
+      <c r="D5" s="10" t="inlineStr">
+        <is>
+          <t>MINUSC</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>Objeto/cosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>PErro</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>perro</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>MINUSC</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>Objeto/cosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>F.b.I</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>F.B.I</t>
+        </is>
+      </c>
+      <c r="D7" s="11" t="inlineStr">
+        <is>
+          <t>MAYUSC</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>Acrónimo/aviso</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>pRoHIBIDO pASAR</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>PROHIBIDO PASAR</t>
+        </is>
+      </c>
+      <c r="D8" s="12" t="inlineStr">
+        <is>
+          <t>MAYUSC</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>Acrónimo/aviso</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>fERNanDa cRUZ</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Fernanda Cruz</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
         <is>
           <t>NOMPROPIO</t>
         </is>
       </c>
-      <c r="E5" s="8" t="inlineStr">
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>Persona</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>VEnTAS</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>Ventas</t>
-        </is>
-      </c>
-      <c r="D6" s="10" t="inlineStr">
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>SiLla</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>silla</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="inlineStr">
         <is>
           <t>MINUSC</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E10" s="8" t="inlineStr">
         <is>
           <t>Objeto/cosa</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="B7" s="8" t="inlineStr">
-        <is>
-          <t>markEtinG</t>
-        </is>
-      </c>
-      <c r="C7" s="8" t="inlineStr">
-        <is>
-          <t>Marketing</t>
-        </is>
-      </c>
-      <c r="D7" s="9" t="inlineStr">
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>EdsOn CoVaRRubiaS</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Edson Covarrubias</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
         <is>
           <t>NOMPROPIO</t>
         </is>
       </c>
-      <c r="E7" s="8" t="inlineStr">
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>Persona</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>Ceo</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="D12" s="12" t="inlineStr">
+        <is>
+          <t>MAYUSC</t>
+        </is>
+      </c>
+      <c r="E12" s="8" t="inlineStr">
+        <is>
+          <t>Acrónimo/aviso</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>CasCO</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>casco</t>
+        </is>
+      </c>
+      <c r="D13" s="10" t="inlineStr">
+        <is>
+          <t>MINUSC</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
         <is>
           <t>Objeto/cosa</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>F.b.i</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>FBI</t>
-        </is>
-      </c>
-      <c r="D8" s="11" t="inlineStr">
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>VENTiLaDor</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>ventilador</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="inlineStr">
+        <is>
+          <t>MINUSC</t>
+        </is>
+      </c>
+      <c r="E14" s="8" t="inlineStr">
+        <is>
+          <t>Objeto/cosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>JoEl COBIan</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Joel Cobian</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>NOMPROPIO</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>Persona</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="7" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>IVA</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>IVA</t>
+        </is>
+      </c>
+      <c r="D16" s="12" t="inlineStr">
         <is>
           <t>MAYUSC</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>Acrónimo</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B9" s="8" t="inlineStr">
-        <is>
-          <t>pRoHIBIDO pASAR</t>
-        </is>
-      </c>
-      <c r="C9" s="8" t="inlineStr">
-        <is>
-          <t>Prohibido Pasar</t>
-        </is>
-      </c>
-      <c r="D9" s="12" t="inlineStr">
-        <is>
-          <t>MAYUSC</t>
-        </is>
-      </c>
-      <c r="E9" s="8" t="inlineStr">
-        <is>
-          <t>Aviso</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>fERnAnDa cRUz</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>Fernanda Cruz</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
+      <c r="E16" s="8" t="inlineStr">
+        <is>
+          <t>Acrónimo/aviso</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>EL UnIVeRSaL</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>El Universal</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
         <is>
           <t>NOMPROPIO</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr">
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>Nombre propio/periódico</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>VIcToR cAMPOs</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>Victor Campos</t>
+        </is>
+      </c>
+      <c r="D18" s="13" t="inlineStr">
+        <is>
+          <t>NOMPROPIO</t>
+        </is>
+      </c>
+      <c r="E18" s="8" t="inlineStr">
         <is>
           <t>Persona</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="B11" s="8" t="inlineStr">
-        <is>
-          <t>sILla</t>
-        </is>
-      </c>
-      <c r="C11" s="8" t="inlineStr">
-        <is>
-          <t>Silla</t>
-        </is>
-      </c>
-      <c r="D11" s="9" t="inlineStr">
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>CARro</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>carro</t>
+        </is>
+      </c>
+      <c r="D19" s="10" t="inlineStr">
+        <is>
+          <t>MINUSC</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>Objeto/cosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>CeLULAR</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>celular</t>
+        </is>
+      </c>
+      <c r="D20" s="9" t="inlineStr">
+        <is>
+          <t>MINUSC</t>
+        </is>
+      </c>
+      <c r="E20" s="8" t="inlineStr">
+        <is>
+          <t>Objeto/cosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>VICtor MaNUEl VIceNTe</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>Víctor Manuel Vicente</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
         <is>
           <t>NOMPROPIO</t>
         </is>
       </c>
-      <c r="E11" s="8" t="inlineStr">
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>Persona</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>GOLondRinA</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>golondrina</t>
+        </is>
+      </c>
+      <c r="D22" s="9" t="inlineStr">
+        <is>
+          <t>MINUSC</t>
+        </is>
+      </c>
+      <c r="E22" s="8" t="inlineStr">
         <is>
           <t>Objeto/cosa</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>EdSOn CoVaRruBias</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>Edson Covarrubias</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>NOMPROPIO</t>
-        </is>
-      </c>
-      <c r="E12" s="5" t="inlineStr">
-        <is>
-          <t>Persona</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="B13" s="8" t="inlineStr">
-        <is>
-          <t>Ceo</t>
-        </is>
-      </c>
-      <c r="C13" s="8" t="inlineStr">
-        <is>
-          <t>Ceo</t>
-        </is>
-      </c>
-      <c r="D13" s="12" t="inlineStr">
-        <is>
-          <t>MAYUSC</t>
-        </is>
-      </c>
-      <c r="E13" s="8" t="inlineStr">
-        <is>
-          <t>Acrónimo</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t>CasCO</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>Casco</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="inlineStr">
-        <is>
-          <t>NOMPROPIO</t>
-        </is>
-      </c>
-      <c r="E14" s="5" t="inlineStr">
-        <is>
-          <t>Objeto/cosa</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="7" t="n">
-        <v>12</v>
-      </c>
-      <c r="B15" s="8" t="inlineStr">
-        <is>
-          <t>VENTiLaDor</t>
-        </is>
-      </c>
-      <c r="C15" s="8" t="inlineStr">
-        <is>
-          <t>Ventilador</t>
-        </is>
-      </c>
-      <c r="D15" s="9" t="inlineStr">
-        <is>
-          <t>NOMPROPIO</t>
-        </is>
-      </c>
-      <c r="E15" s="8" t="inlineStr">
-        <is>
-          <t>Objeto/cosa</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="B16" s="5" t="inlineStr">
-        <is>
-          <t>JoEl COBIan</t>
-        </is>
-      </c>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t>Joel Cobian</t>
-        </is>
-      </c>
-      <c r="D16" s="6" t="inlineStr">
-        <is>
-          <t>NOMPROPIO</t>
-        </is>
-      </c>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t>Persona</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="7" t="n">
-        <v>14</v>
-      </c>
-      <c r="B17" s="8" t="inlineStr">
-        <is>
-          <t>IVA</t>
-        </is>
-      </c>
-      <c r="C17" s="8" t="inlineStr">
-        <is>
-          <t>Iva</t>
-        </is>
-      </c>
-      <c r="D17" s="12" t="inlineStr">
-        <is>
-          <t>MAYUSC</t>
-        </is>
-      </c>
-      <c r="E17" s="8" t="inlineStr">
-        <is>
-          <t>Acrónimo</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>EL UnIVeRSaL</t>
-        </is>
-      </c>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>El Universal</t>
-        </is>
-      </c>
-      <c r="D18" s="6" t="inlineStr">
-        <is>
-          <t>NOMPROPIO</t>
-        </is>
-      </c>
-      <c r="E18" s="5" t="inlineStr">
-        <is>
-          <t>Nombre propio</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="7" t="n">
-        <v>16</v>
-      </c>
-      <c r="B19" s="8" t="inlineStr">
-        <is>
-          <t>VIcToR cAMPOs</t>
-        </is>
-      </c>
-      <c r="C19" s="8" t="inlineStr">
-        <is>
-          <t>Victor Campos</t>
-        </is>
-      </c>
-      <c r="D19" s="9" t="inlineStr">
-        <is>
-          <t>NOMPROPIO</t>
-        </is>
-      </c>
-      <c r="E19" s="8" t="inlineStr">
-        <is>
-          <t>Persona</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>CARro</t>
-        </is>
-      </c>
-      <c r="C20" s="5" t="inlineStr">
-        <is>
-          <t>Carro</t>
-        </is>
-      </c>
-      <c r="D20" s="6" t="inlineStr">
-        <is>
-          <t>NOMPROPIO</t>
-        </is>
-      </c>
-      <c r="E20" s="5" t="inlineStr">
-        <is>
-          <t>Objeto/cosa</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="7" t="n">
-        <v>18</v>
-      </c>
-      <c r="B21" s="8" t="inlineStr">
-        <is>
-          <t>CeLULAR</t>
-        </is>
-      </c>
-      <c r="C21" s="8" t="inlineStr">
-        <is>
-          <t>Celular</t>
-        </is>
-      </c>
-      <c r="D21" s="9" t="inlineStr">
-        <is>
-          <t>NOMPROPIO</t>
-        </is>
-      </c>
-      <c r="E21" s="8" t="inlineStr">
-        <is>
-          <t>Objeto/cosa</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="4" t="n">
-        <v>19</v>
-      </c>
-      <c r="B22" s="5" t="inlineStr">
-        <is>
-          <t>ViCtOr MaNuEl ViCENte</t>
-        </is>
-      </c>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t>Victor Manuel Vicente</t>
-        </is>
-      </c>
-      <c r="D22" s="6" t="inlineStr">
-        <is>
-          <t>NOMPROPIO</t>
-        </is>
-      </c>
-      <c r="E22" s="5" t="inlineStr">
-        <is>
-          <t>Persona</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="22" customHeight="1">
-      <c r="A23" s="7" t="n">
-        <v>20</v>
-      </c>
-      <c r="B23" s="8" t="inlineStr">
-        <is>
-          <t>GoLonDRinA</t>
-        </is>
-      </c>
-      <c r="C23" s="8" t="inlineStr">
-        <is>
-          <t>Golondrina</t>
-        </is>
-      </c>
-      <c r="D23" s="9" t="inlineStr">
-        <is>
-          <t>NOMPROPIO</t>
-        </is>
-      </c>
-      <c r="E23" s="8" t="inlineStr">
-        <is>
-          <t>Animal</t>
+    <row r="25">
+      <c r="A25" s="14" t="inlineStr">
+        <is>
+          <t>Criterio:</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="15" t="inlineStr">
+        <is>
+          <t>Personas y nombres propios  →  NOMPROPIO</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="15" t="inlineStr">
+        <is>
+          <t>Objetos/cosas  →  MINUSC</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="15" t="inlineStr">
+        <is>
+          <t>Acrónimos y avisos  →  MAYUSC</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:E23"/>
-  <mergeCells count="1">
+  <autoFilter ref="A2:E22"/>
+  <mergeCells count="5">
+    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="A25:E25"/>
     <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A27:E27"/>
   </mergeCells>
-  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
-  <pageSetup orientation="portrait" paperSize="3" fitToHeight="1" fitToWidth="1"/>
+  <pageMargins left="0.45" right="0.45" top="0.45" bottom="0.45" header="0.2" footer="0.2"/>
+  <pageSetup orientation="landscape" paperSize="3" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
 </file>